--- a/fix-mapping-entete-duplicate-targets/ig/FRParticipantHeaderLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRParticipantHeaderLMCDAFHIR.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:43:57+00:00</t>
+    <t>2026-09-02T12:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>FRLMParticipant.participant.participantOrganisation</t>
+  </si>
+  <si>
+    <t>FRLMOrganisation</t>
   </si>
   <si>
     <t>FRLMParticipant.participant.participantDevice</t>
@@ -560,7 +563,9 @@
       <c r="A8" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" t="s" s="2">
+        <v>46</v>
+      </c>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
@@ -571,7 +576,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -620,7 +625,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -628,27 +633,27 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -690,7 +695,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -705,33 +710,33 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -744,7 +749,7 @@
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -757,7 +762,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -770,7 +775,7 @@
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -783,7 +788,7 @@
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -791,25 +796,27 @@
       <c r="A10" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" t="s" s="2">
+        <v>46</v>
+      </c>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2"/>
     </row>

--- a/fix-mapping-entete-duplicate-targets/ig/FRParticipantHeaderLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRParticipantHeaderLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:54:48+00:00</t>
+    <t>2026-09-02T15:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRParticipantHeaderLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRParticipantHeaderLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:48:56+00:00</t>
+    <t>2026-09-03T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRParticipantHeaderLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRParticipantHeaderLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:02:14+00:00</t>
+    <t>2026-09-03T10:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRParticipantHeaderLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRParticipantHeaderLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:35:28+00:00</t>
+    <t>2026-09-04T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
